--- a/BoM/BoM.xlsx
+++ b/BoM/BoM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programs\AVR32EB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programs\AVR32EB\Release v1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE03776-08AD-48B9-8069-3E97C266E884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A8C60E-3451-4B8A-B874-2910A6CE2ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30750" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -595,7 +595,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
